--- a/zscore_przyklad_olaf.xlsx
+++ b/zscore_przyklad_olaf.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Lp.</t>
   </si>
@@ -68,6 +68,15 @@
   </si>
   <si>
     <t>2011-12-01</t>
+  </si>
+  <si>
+    <t>Data pomiaru</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
   </si>
 </sst>
 </file>
@@ -425,10 +434,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,8 +456,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -467,8 +479,11 @@
       <c r="F2">
         <v>130</v>
       </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -487,8 +502,11 @@
       <c r="F3">
         <v>135</v>
       </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -507,8 +525,11 @@
       <c r="F4">
         <v>140</v>
       </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -527,8 +548,11 @@
       <c r="F5">
         <v>150</v>
       </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -546,6 +570,9 @@
       </c>
       <c r="F6">
         <v>132</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
